--- a/题库导入标准模板.xlsx
+++ b/题库导入标准模板.xlsx
@@ -22,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -44,6 +44,10 @@
     <font>
       <name val="Arial"/>
       <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -101,7 +105,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -116,6 +120,15 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -483,304 +496,354 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE3"/>
+  <dimension ref="A1:AK3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="24" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="10" customWidth="1" min="15" max="15"/>
-    <col width="48" customWidth="1" min="16" max="16"/>
-    <col width="50" customWidth="1" min="17" max="17"/>
-    <col width="50" customWidth="1" min="18" max="18"/>
-    <col width="28" customWidth="1" min="19" max="19"/>
-    <col width="28" customWidth="1" min="20" max="20"/>
-    <col width="24" customWidth="1" min="21" max="21"/>
-    <col width="24" customWidth="1" min="22" max="22"/>
-    <col width="24" customWidth="1" min="23" max="23"/>
-    <col width="46" customWidth="1" min="24" max="24"/>
-    <col width="36" customWidth="1" min="25" max="25"/>
-    <col width="56" customWidth="1" min="26" max="26"/>
-    <col width="28" customWidth="1" min="27" max="27"/>
-    <col width="30" customWidth="1" min="28" max="28"/>
-    <col width="48" customWidth="1" min="29" max="29"/>
-    <col width="48" customWidth="1" min="30" max="30"/>
-    <col width="28" customWidth="1" min="31" max="31"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="19" customWidth="1" min="9" max="9"/>
+    <col width="19" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="17" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="46" customWidth="1" min="20" max="20"/>
+    <col width="48" customWidth="1" min="21" max="21"/>
+    <col width="48" customWidth="1" min="22" max="22"/>
+    <col width="16" customWidth="1" min="23" max="23"/>
+    <col width="18" customWidth="1" min="24" max="24"/>
+    <col width="16" customWidth="1" min="25" max="25"/>
+    <col width="17" customWidth="1" min="26" max="26"/>
+    <col width="19" customWidth="1" min="27" max="27"/>
+    <col width="44" customWidth="1" min="28" max="28"/>
+    <col width="34" customWidth="1" min="29" max="29"/>
+    <col width="60" customWidth="1" min="30" max="30"/>
+    <col width="12" customWidth="1" min="31" max="31"/>
+    <col width="32" customWidth="1" min="32" max="32"/>
+    <col width="40" customWidth="1" min="33" max="33"/>
+    <col width="14" customWidth="1" min="34" max="34"/>
+    <col width="19" customWidth="1" min="35" max="35"/>
+    <col width="24" customWidth="1" min="36" max="36"/>
+    <col width="36" customWidth="1" min="37" max="37"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>suiteId</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="6" t="inlineStr">
+        <is>
+          <t>suiteKey</t>
+        </is>
+      </c>
+      <c r="C1" s="6" t="inlineStr">
         <is>
           <t>suiteName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="6" t="inlineStr">
         <is>
           <t>examDate</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="6" t="inlineStr">
         <is>
           <t>batch</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="6" t="inlineStr">
         <is>
           <t>province</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="6" t="inlineStr">
         <is>
           <t>position</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="6" t="inlineStr">
+        <is>
+          <t>answerScoreTotal</t>
+        </is>
+      </c>
+      <c r="I1" s="6" t="inlineStr">
+        <is>
+          <t>appearanceScore</t>
+        </is>
+      </c>
+      <c r="J1" s="6" t="inlineStr">
+        <is>
+          <t>suiteTotalScore</t>
+        </is>
+      </c>
+      <c r="K1" s="6" t="inlineStr">
         <is>
           <t>totalScore</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="L1" s="6" t="inlineStr">
         <is>
           <t>questionNo</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="M1" s="6" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="N1" s="6" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="O1" s="6" t="inlineStr">
         <is>
           <t>dimension</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="P1" s="6" t="inlineStr">
         <is>
           <t>fullScore</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="Q1" s="6" t="inlineStr">
         <is>
           <t>questionScore</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="R1" s="6" t="inlineStr">
         <is>
           <t>prepTime</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="S1" s="6" t="inlineStr">
         <is>
           <t>answerTime</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="T1" s="6" t="inlineStr">
         <is>
           <t>question</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="U1" s="6" t="inlineStr">
         <is>
           <t>dimensions_json</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="V1" s="6" t="inlineStr">
         <is>
           <t>scoringPoints_json</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="W1" s="6" t="inlineStr">
         <is>
           <t>coreKeywords</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="X1" s="6" t="inlineStr">
         <is>
           <t>strongKeywords</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="Y1" s="6" t="inlineStr">
         <is>
           <t>weakKeywords</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="Z1" s="6" t="inlineStr">
         <is>
           <t>bonusKeywords</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AA1" s="6" t="inlineStr">
         <is>
           <t>penaltyKeywords</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AB1" s="6" t="inlineStr">
         <is>
           <t>scoringCriteria</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AC1" s="6" t="inlineStr">
         <is>
           <t>deductionRules</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AD1" s="6" t="inlineStr">
         <is>
           <t>referenceAnswer</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AE1" s="6" t="inlineStr">
         <is>
           <t>tags</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AF1" s="6" t="inlineStr">
         <is>
           <t>sourceDocument</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AG1" s="6" t="inlineStr">
+        <is>
+          <t>sourceTitleRaw</t>
+        </is>
+      </c>
+      <c r="AH1" s="6" t="inlineStr">
+        <is>
+          <t>sourcePage</t>
+        </is>
+      </c>
+      <c r="AI1" s="6" t="inlineStr">
         <is>
           <t>scoreBands_json</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AJ1" s="6" t="inlineStr">
         <is>
           <t>regressionCases_json</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AK1" s="6" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>AH-SYDW-2026-001</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="7" t="inlineStr">
+        <is>
+          <t>AH-SYDW-2026-001</t>
+        </is>
+      </c>
+      <c r="C2" s="7" t="inlineStr">
         <is>
           <t>2026年安徽事业单位面试全真模拟卷一</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="D2" s="7" t="inlineStr">
         <is>
           <t>2026-01-01</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="E2" s="7" t="inlineStr">
         <is>
           <t>第一批次</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="F2" s="7" t="inlineStr">
         <is>
           <t>安徽</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="G2" s="7" t="inlineStr">
         <is>
           <t>综合管理岗</t>
         </is>
       </c>
-      <c r="G2" s="2" t="n">
+      <c r="H2" s="7" t="n">
+        <v>95</v>
+      </c>
+      <c r="I2" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="J2" s="7" t="n">
         <v>100</v>
       </c>
-      <c r="H2" s="2" t="n">
+      <c r="K2" s="7" t="n">
+        <v>100</v>
+      </c>
+      <c r="L2" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="M2" s="7" t="inlineStr">
         <is>
           <t>AH-SYDW-20260101-01</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="N2" s="7" t="inlineStr">
         <is>
           <t>综合分析·基层治理</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="O2" s="7" t="inlineStr">
         <is>
           <t>analysis</t>
         </is>
       </c>
-      <c r="L2" s="2" t="n">
+      <c r="P2" s="7" t="n">
         <v>25</v>
       </c>
-      <c r="M2" s="2" t="n">
+      <c r="Q2" s="7" t="n">
         <v>25</v>
       </c>
-      <c r="N2" s="2" t="n">
+      <c r="R2" s="7" t="n">
         <v>90</v>
       </c>
-      <c r="O2" s="2" t="n">
+      <c r="S2" s="7" t="n">
         <v>180</v>
       </c>
-      <c r="P2" s="2" t="inlineStr">
+      <c r="T2" s="7" t="inlineStr">
         <is>
           <t>某地推进基层治理数字化，但部分群众反映线上流程复杂、线下窗口减少。对此你怎么看？（25分）</t>
         </is>
       </c>
-      <c r="Q2" s="2" t="inlineStr">
+      <c r="U2" s="7" t="inlineStr">
         <is>
           <t>[{"name": "观点明确，能辩证看待数字治理与群众便利的关系", "score": 5}, {"name": "分析充分，能指出效率提升、适老化不足、线下兜底等关键矛盾", "score": 8}, {"name": "对策可行，能提出流程优化、帮办代办、保留窗口、反馈闭环等措施", "score": 8}, {"name": "表达清晰，结构完整，语言规范", "score": 4}]</t>
         </is>
       </c>
-      <c r="R2" s="2" t="inlineStr">
+      <c r="V2" s="7" t="inlineStr">
         <is>
           <t>[{"content": "观点明确，能辩证看待数字治理与群众便利的关系", "score": 5}, {"content": "分析充分，能指出效率提升、适老化不足、线下兜底等关键矛盾", "score": 8}, {"content": "对策可行，能提出流程优化、帮办代办、保留窗口、反馈闭环等措施", "score": 8}, {"content": "表达清晰，结构完整，语言规范", "score": 4}]</t>
         </is>
       </c>
-      <c r="S2" s="2" t="inlineStr">
+      <c r="W2" s="7" t="inlineStr">
         <is>
           <t>基层治理；数字化；群众便利；线下兜底</t>
         </is>
       </c>
-      <c r="T2" s="2" t="inlineStr">
+      <c r="X2" s="7" t="inlineStr">
         <is>
           <t>适老化；帮办代办；反馈闭环</t>
         </is>
       </c>
-      <c r="U2" s="2" t="inlineStr">
+      <c r="Y2" s="7" t="inlineStr">
         <is>
           <t>窗口服务；流程优化</t>
         </is>
       </c>
-      <c r="V2" s="2" t="inlineStr">
+      <c r="Z2" s="7" t="inlineStr">
         <is>
           <t>以人民为中心；长效机制；数据赋能</t>
         </is>
       </c>
-      <c r="W2" s="2" t="inlineStr">
+      <c r="AA2" s="7" t="inlineStr">
         <is>
           <t>只谈技术不谈群众；脱离题意；对策空泛</t>
         </is>
       </c>
-      <c r="X2" s="2" t="inlineStr">
+      <c r="AB2" s="7" t="inlineStr">
         <is>
           <t>观点明确（5分）：能指出数字治理应服务群众，而不是让群众迁就系统。
 分析充分（8分）：能同时看到效率价值和特殊群体使用门槛。
@@ -788,184 +851,218 @@
 表达清晰（4分）：结构完整，语言规范。</t>
         </is>
       </c>
-      <c r="Y2" s="2" t="inlineStr">
+      <c r="AC2" s="7" t="inlineStr">
         <is>
           <t>完全脱离题意扣8-12分。
 只有表态无分析扣4-6分。
 无具体对策扣3-5分。</t>
         </is>
       </c>
-      <c r="Z2" s="2" t="inlineStr">
+      <c r="AD2" s="7" t="inlineStr">
         <is>
           <t>参考作答应围绕数字治理的初衷、当前痛点和改进路径展开。首先肯定数字化提升办理效率，但也要看到部分群众尤其老年群体存在不会用、不敢用、用不好等问题。下一步应优化线上流程，保留必要线下窗口，建立帮办代办机制，并通过群众反馈持续迭代系统。</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
+      <c r="AE2" s="7" t="inlineStr">
         <is>
           <t>安徽；事业单位；综合分析；基层治理；全真模拟</t>
         </is>
       </c>
-      <c r="AB2" s="2" t="inlineStr">
+      <c r="AF2" s="7" t="inlineStr">
         <is>
           <t>2026安徽事业单位面试真题.docx</t>
         </is>
       </c>
-      <c r="AC2" s="2" t="inlineStr">
+      <c r="AG2" s="7" t="inlineStr">
+        <is>
+          <t>2026年安徽事业单位面试全真模拟卷一</t>
+        </is>
+      </c>
+      <c r="AH2" s="7" t="inlineStr">
+        <is>
+          <t>第1页</t>
+        </is>
+      </c>
+      <c r="AI2" s="7" t="inlineStr">
         <is>
           <t>[{"label": "严重偏离", "minScore": 0, "maxScore": 13.7, "description": "观点错误或明显脱题，缺少有效分析。"}, {"label": "基本合格", "minScore": 13.8, "maxScore": 17.5, "description": "能回应题目，但分析和对策较泛。"}, {"label": "微微偏离", "minScore": 17.6, "maxScore": 21.2, "description": "主线正确，部分要点展开不足。"}, {"label": "预期范围", "minScore": 21.3, "maxScore": 25, "description": "结构完整、要点充分、表达自然。"}]</t>
         </is>
       </c>
-      <c r="AD2" s="2" t="inlineStr">
+      <c r="AJ2" s="7" t="inlineStr">
         <is>
           <t>[{"caseId": "AH-SYDW-20260101-01-A", "answerType": "high", "expectedMinScore": 21, "expectedMaxScore": 25, "answer": "示例高分作答文本。"}, {"caseId": "AH-SYDW-20260101-01-B", "answerType": "low", "expectedMinScore": 0, "expectedMaxScore": 14, "answer": "示例低分作答文本。"}]</t>
         </is>
       </c>
-      <c r="AE2" s="2" t="inlineStr">
+      <c r="AK2" s="7" t="inlineStr">
         <is>
           <t>每题分值以 questionScore/fullScore 为准；dimensions/scoringPoints 分值建议合计等于该题满分。</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>AH-SYDW-2026-001</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>AH-SYDW-2026-001</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
         <is>
           <t>2026年安徽事业单位面试全真模拟卷一</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="D3" s="7" t="inlineStr">
         <is>
           <t>2026-01-01</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="E3" s="7" t="inlineStr">
         <is>
           <t>第一批次</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="F3" s="7" t="inlineStr">
         <is>
           <t>安徽</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="G3" s="7" t="inlineStr">
         <is>
           <t>综合管理岗</t>
         </is>
       </c>
-      <c r="G3" s="2" t="n">
+      <c r="H3" s="7" t="n">
+        <v>95</v>
+      </c>
+      <c r="I3" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="J3" s="7" t="n">
         <v>100</v>
       </c>
-      <c r="H3" s="2" t="n">
+      <c r="K3" s="7" t="n">
+        <v>100</v>
+      </c>
+      <c r="L3" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="M3" s="7" t="inlineStr">
         <is>
           <t>AH-SYDW-20260101-02</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="N3" s="7" t="inlineStr">
         <is>
           <t>组织管理·调研宣传</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="O3" s="7" t="inlineStr">
         <is>
           <t>practical</t>
         </is>
       </c>
-      <c r="L3" s="2" t="n">
+      <c r="P3" s="7" t="n">
         <v>25</v>
       </c>
-      <c r="M3" s="2" t="n">
+      <c r="Q3" s="7" t="n">
         <v>25</v>
       </c>
-      <c r="N3" s="2" t="n">
+      <c r="R3" s="7" t="n">
         <v>90</v>
       </c>
-      <c r="O3" s="2" t="n">
+      <c r="S3" s="7" t="n">
         <v>180</v>
       </c>
-      <c r="P3" s="2" t="inlineStr">
+      <c r="T3" s="7" t="inlineStr">
         <is>
           <t>单位准备开展便民政策宣传活动，领导交给你组织，你会怎么做？（25分）</t>
         </is>
       </c>
-      <c r="Q3" s="2" t="inlineStr">
+      <c r="U3" s="7" t="inlineStr">
         <is>
           <t>[{"name": "目标明确，能围绕群众知晓和政策落地设计活动", "score": 6}, {"name": "流程完整，包含前期调研、对象分层、渠道安排、现场保障", "score": 9}, {"name": "效果评估充分，能收集反馈并形成改进建议", "score": 6}, {"name": "表达有条理，执行意识强", "score": 4}]</t>
         </is>
       </c>
-      <c r="R3" s="2" t="inlineStr">
+      <c r="V3" s="7" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="S3" s="2" t="inlineStr">
+      <c r="W3" s="7" t="inlineStr">
         <is>
           <t>便民政策；宣传活动；群众需求；效果反馈</t>
         </is>
       </c>
-      <c r="T3" s="2" t="inlineStr">
+      <c r="X3" s="7" t="inlineStr">
         <is>
           <t>分层分类；线上线下结合；现场答疑</t>
         </is>
       </c>
-      <c r="U3" s="2" t="inlineStr">
+      <c r="Y3" s="7" t="inlineStr">
         <is>
           <t>物料准备；部门协同</t>
         </is>
       </c>
-      <c r="V3" s="2" t="inlineStr">
+      <c r="Z3" s="7" t="inlineStr">
         <is>
           <t>闭环评估；精准触达</t>
         </is>
       </c>
-      <c r="W3" s="2" t="inlineStr">
+      <c r="AA3" s="7" t="inlineStr">
         <is>
           <t>流程缺失；没有群众视角</t>
         </is>
       </c>
-      <c r="X3" s="2" t="inlineStr">
+      <c r="AB3" s="7" t="inlineStr">
         <is>
           <t>按准备、实施、总结三个阶段评分。</t>
         </is>
       </c>
-      <c r="Y3" s="2" t="inlineStr">
+      <c r="AC3" s="7" t="inlineStr">
         <is>
           <t>无具体执行步骤扣4-8分。</t>
         </is>
       </c>
-      <c r="Z3" s="2" t="inlineStr">
+      <c r="AD3" s="7" t="inlineStr">
         <is>
           <t>参考作答略。</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
+      <c r="AE3" s="7" t="inlineStr">
         <is>
           <t>安徽；事业单位；组织管理；全真模拟</t>
         </is>
       </c>
-      <c r="AB3" s="2" t="inlineStr">
+      <c r="AF3" s="7" t="inlineStr">
         <is>
           <t>2026安徽事业单位面试真题.docx</t>
         </is>
       </c>
-      <c r="AC3" s="2" t="inlineStr">
+      <c r="AG3" s="7" t="inlineStr">
+        <is>
+          <t>2026年安徽事业单位面试全真模拟卷一</t>
+        </is>
+      </c>
+      <c r="AH3" s="7" t="inlineStr">
+        <is>
+          <t>第1页</t>
+        </is>
+      </c>
+      <c r="AI3" s="7" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AD3" s="2" t="inlineStr">
+      <c r="AJ3" s="7" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AE3" s="2" t="inlineStr"/>
+      <c r="AK3" s="7" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AE3"/>
@@ -987,7 +1084,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D32"/>
+  <dimension ref="A1:D38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1697,6 +1794,138 @@
       <c r="D32" s="2" t="inlineStr">
         <is>
           <t>维护说明</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t>suiteKey</t>
+        </is>
+      </c>
+      <c r="B33" s="8" t="inlineStr">
+        <is>
+          <t>套题分组键</t>
+        </is>
+      </c>
+      <c r="C33" s="8" t="inlineStr">
+        <is>
+          <t>建议</t>
+        </is>
+      </c>
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t>默认等同 suiteId；脚本从题号前缀自动提取时会写入该字段</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="8" t="inlineStr">
+        <is>
+          <t>answerScoreTotal</t>
+        </is>
+      </c>
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>整套答题分</t>
+        </is>
+      </c>
+      <c r="C34" s="8" t="inlineStr">
+        <is>
+          <t>建议</t>
+        </is>
+      </c>
+      <c r="D34" s="8" t="inlineStr">
+        <is>
+          <t>整套题目作答分合计，如 95</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="8" t="inlineStr">
+        <is>
+          <t>appearanceScore</t>
+        </is>
+      </c>
+      <c r="B35" s="8" t="inlineStr">
+        <is>
+          <t>仪态分</t>
+        </is>
+      </c>
+      <c r="C35" s="8" t="inlineStr">
+        <is>
+          <t>建议</t>
+        </is>
+      </c>
+      <c r="D35" s="8" t="inlineStr">
+        <is>
+          <t>总分中除答题分外的仪态/表达状态分，如 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="8" t="inlineStr">
+        <is>
+          <t>suiteTotalScore</t>
+        </is>
+      </c>
+      <c r="B36" s="8" t="inlineStr">
+        <is>
+          <t>套题总分</t>
+        </is>
+      </c>
+      <c r="C36" s="8" t="inlineStr">
+        <is>
+          <t>建议</t>
+        </is>
+      </c>
+      <c r="D36" s="8" t="inlineStr">
+        <is>
+          <t>整套满分，通常为 100；与 totalScore 保持一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="8" t="inlineStr">
+        <is>
+          <t>sourceTitleRaw</t>
+        </is>
+      </c>
+      <c r="B37" s="8" t="inlineStr">
+        <is>
+          <t>原始套题标题</t>
+        </is>
+      </c>
+      <c r="C37" s="8" t="inlineStr">
+        <is>
+          <t>建议</t>
+        </is>
+      </c>
+      <c r="D37" s="8" t="inlineStr">
+        <is>
+          <t>Word 文档中单独成行的真实套题标题原文</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="8" t="inlineStr">
+        <is>
+          <t>sourcePage</t>
+        </is>
+      </c>
+      <c r="B38" s="8" t="inlineStr">
+        <is>
+          <t>来源页码/位置</t>
+        </is>
+      </c>
+      <c r="C38" s="8" t="inlineStr">
+        <is>
+          <t>可选</t>
+        </is>
+      </c>
+      <c r="D38" s="8" t="inlineStr">
+        <is>
+          <t>如 第1页、P12、微信群截图2 等，便于追溯</t>
         </is>
       </c>
     </row>
@@ -1917,7 +2146,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2020,6 +2249,18 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>真实标题可抽取</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>真实套题标题必须单独成行，并放在本套题第一道题号前；不要把标题和题号写在同一行</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
